--- a/data_extactor/batch_10_fa/trimmed/batch_0066_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0066_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | ریاضیات | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | اقتصاد و حسابداری | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | اقتصاد و حسابداری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | مهارت در کار با اعداد | تشخیص گفتار | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | دید نزدیک</t>
+          <t>درک شفاهی | توانایی عددی | تشخیص گفتار | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان وصول مطالبات | صندوق‌داران | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات مشتریان | کارشناسان اعطای تسهیلات | کارشناسان افتتاح حساب | متصدیان امور اداری و دفتری عمومی</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | صندوق‌داران | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | متصدیان امور دفتری و امور عمومی اداری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | حقوق و امور دولتی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک کتبی | استدلال ریاضی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کاردان‌ها و کارشناسان حسابداری و حسابرسی | کارشناسان صدور صورت‌حساب و ثبت اسناد مالی | کارشناسان وصول مطالبات | کارشناسان حقوق و دستمزد و ثبت کارکرد | کارشناسان کارپردازی و خرید | تحویل‌داران و متصدیان امور بانکی | کارشناسان افتتاح حساب</t>
+          <t>کارمندان دفترداری، حسابداری و امور حسابرسی | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | کارمندان تدارکات و کارپردازی | تحویل‌داران و متصدیان امور بانکی | متصدیان افتتاح حساب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | اداری و سازمانی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات | مهارت در کار با اعداد</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | توانایی عددی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کاردان‌ها و کارشناسان حسابداری و حسابرسی | کارشناسان تحلیل اعتبار و تسهیلات | کارشناسان خدمات مشتریان | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان افتتاح حساب | کارگزاران و نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | تحویل‌داران و متصدیان امور بانکی</t>
+          <t>کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | تحلیل‌گران مالی و سرمایه‌گذاری | متصدیان افتتاح حساب | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>اداری و سازمانی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان وصول مطالبات | کارشناسان خدمات مشتریان | کارشناسان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیران ارشد | متصدیان بایگانی | متصدیان امور اداری و دفتری عمومی | منشی‌ها و دستیاران اداری (به‌جز حقوقی، پزشکی و اجرایی)</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | متصدیان امور دفتری و امور عمومی اداری | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اداری و سازمانی | حقوق و امور دولتی | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | قانون و دولت | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | درک کتبی | وضوح گفتار | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و گزارشگران جلسات و دادگاه | مسئولان دفاتر و دستیاران اجرایی مدیران ارشد | متصدیان بایگانی | منشی‌ها و مسئولان دفاتر حقوقی | دستیاران حقوقی و کارشناسان پشتیبانی امور وکالت | مسئولان پذیرش و راهنمای مراجعان</t>
+          <t>کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی | متصدیان پذیرش و اطلاعات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | حقوق و امور دولتی | اداری و سازمانی | اقتصاد و حسابداری | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | قانون و دولت | اداری | اقتصاد و حسابداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | درک کتبی | دید نزدیک | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | درک کتبی | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان وصول مطالبات | کارشناسان تحلیل اعتبار و تسهیلات | مشاوران امور اعتباری و تسهیلات | کارشناسان خدمات مشتریان | کارشناسان مصاحبه و بررسی وام | کارشناسان اعطای تسهیلات | تحویل‌داران و متصدیان امور بانکی</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | تحلیل‌گران اعتبارات و تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | فروش و بازاریابی | ریاضیات | اداری و سازمانی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | فروش و بازاریابی | ریاضیات | اداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | بیان کتبی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | بیان کتبی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان وصول مطالبات | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه | کارشناسان ثبت سفارش‌ها | مسئولان پذیرش و راهنمای مراجعان | بازاریابان تلفنی</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان پذیرش و اطلاعات | کارشناسان بازاریابی تلفنی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | اداری و سازمانی | پرسنلی و منابع انسانی | رایانه و الکترونیک | حقوق و امور دولتی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اداری | پرسنل و منابع انسانی | رایانه و الکترونیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان نظارت و انطباق با قوانین و مقررات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات مشتریان | دستیاران منابع انسانی (به‌جز حقوق و دستمزد و ثبت کارکرد) | کارشناسان منابع انسانی | متصدیان مصاحبه و پرسشگری (به‌جز واجدین شرایط و وام) | متصدیان امور اداری و دفتری عمومی</t>
+          <t>کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | متصدیان امور دفتری و امور عمومی اداری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | نظارت | تفکر انتقادی</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>اداری و سازمانی | خدمات مشتریان و خدمات فردی | حقوق و امور دولتی | رایانه و الکترونیک | مخابرات و ارتباطات | ریاضیات</t>
+          <t>اداری | خدمات مشتری و شخصی | قانون و دولت | رایانه و الکترونیک | مخابرات | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | درک کتبی | انعطاف‌پذیری در طبقه‌بندی | درک شفاهی | بیان شفاهی | توجه انتخابی | سرعت ادراک</t>
+          <t>ترتیب‌دهی اطلاعات | درک کتبی | انعطاف‌پذیری دسته‌بندی | درک شفاهی | بیان شفاهی | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>آرشیویست‌ها و کارشناسان مراکز اسناد | متصدیان ورود داده‌ها و اطلاعات | کارشناسان مدیریت اسناد و مدارک | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | متصدیان امور اداری و دفتری عمومی | مسئولان پذیرش و راهنمای مراجعان | منشی‌ها و دستیاران اداری (به‌جز حقوقی، پزشکی و اجرایی)</t>
+          <t>کارشناسان اسناد و آرشیو | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان مدیریت اسناد و مدارک | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | متصدیان امور دفتری و امور عمومی اداری | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | اداری و سازمانی | رایانه و الکترونیک | مدیریت و امور اداری | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | اداری | رایانه و الکترونیک | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دربانان مجلل و راهنمایان اختصاصی میهمانان در هتل | کارشناسان خدمات مشتریان | مدیران اقامتی و هتلداری | متصدیان امور اداری و دفتری عمومی | راهنمایان و متصدیان خدمات مسافران | مسئولان پذیرش و راهنمای مراجعان | متصدیان صدور بلیط، خدمات مسافرتی و رزرواسیون</t>
+          <t>متصدیان تشریفات و خدمات میهمانان | کارشناسان خدمات و پشتیبانی مشتریان | مدیران هتل و مراکز اقامتی | متصدیان امور دفتری و امور عمومی اداری | مهمانداران و متصدیان خدمات مسافران | متصدیان پذیرش و اطلاعات | متصدیان فروش بلیت، رزرواسیون و خدمات سفر</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
